--- a/internal_doc/05.测试设计/story/alter/altercl测试用例（cl基本功能）.xlsx
+++ b/internal_doc/05.测试设计/story/alter/altercl测试用例（cl基本功能）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="205">
   <si>
     <t>name</t>
   </si>
@@ -565,11 +565,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、开启压缩操作成功，查看cl属性信息中压缩类型为设置类型
-2、关闭压缩操作成功，查看cl属性信息中无压缩属性信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>开启压缩，执行插入、查询数据操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -578,11 +573,6 @@
 2、执行插入、查询操作
 3、检查操作结果
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、开启压缩操作成功，查看cl属性信息中压缩类型默认为snappy
-2、数据插入成功，查询数据正确，查看数据按snappy方式压缩（和未开启压缩数据对比）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -602,11 +592,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、切分后，snapshot检查源组和目标组attribute:1,压缩类型为snappy
-2、关闭压缩后，快照查看cl属性中压缩未开启，查看原压缩数据未变化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>使用setAttributes接口开启压缩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -631,27 +616,6 @@
   <si>
     <t>1、sequoiadb集群运行正常
 2、集群中存在cs、cl，且cl中压缩类型为lzw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景a：更新压缩类型成功，查看cl属性中压缩类型为snappy
-场景b：更新压缩类型失败，查看cl属性中压缩类型为原值lzw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、使用setAttributes修改压缩类型为snappy，分别验证如下场景：
-a、cl中没有生成数据字典，更新压缩类型为snappy
-b、cl中存在数据字典，更新压缩类型为snappy
-2、检查操作结果
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、开启压缩，修改压缩类型为lzw，分别验证如下场景：
-a、cl中没有数据，更新压缩类型为lzw
-b、cl中存在数据，更新压缩类型为lzw
-2、检查操作结果
-3、插入数据查看数据压缩情况</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -667,19 +631,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、cl上设置压缩类型为lzw，插入数据刚好达到构建数据字典条件
-2、执行切分（切分后目标组上没有字典）
-3、修改压缩类型为snappy，检查操作结果
-4、truncate删除cl数据
-5、修改压缩类型为snappy，检查操作结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、步骤3中修改失败，返回对应错误信息，查看cl属性中压缩类型未更新
-2、步骤5中修改成功，查看cl属性中压缩类型为snappy类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>未开启压缩，修改压缩类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -849,11 +800,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、truncate操作成功，查看cl中数据为空；
-2、修改压缩类型操作成功，快照（8）查看cl属性信息中压缩类型为lzw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">1、修改失败，返回对应错误信息；查看cl属性信息中EnsureShardingIndex未更新
 2、切分操作成功
 </t>
@@ -895,11 +841,6 @@
     <t xml:space="preserve">1、创建cs，指定Capped为true，创建cl指定Size等属性值
 2、执行cl.setAttributes修改Size属性信息
 3、检查修改结果
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、固定集合修改成功，快照(8)查看cl属性信息中Size值已更新
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -926,12 +867,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、固定集合修改成功，快照(8)查看cl属性信息中OverWrite值已更新
-2、插入记录成功，第一块的数据被覆盖，查询记录数不变
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>普通表修改固定集合属性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1041,11 +976,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>场景a：更新压缩类型成功，查看cl属性中压缩类型为lzw；插入数据后，查看数据有压缩（查看对应数据节点snapshot（4）中的DictionaryCreated参数为true）；数据组中所有节点上cl压缩类型一致
-场景b：更新压缩类型失败，查看cl属性中压缩类型为原值snappy，查看数据按原有方式压缩（查看对应数据节点snapshot（4）中的DictionaryCreated参数为false）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、修改成功，快照（snapshot（8））查看cl属性信息中shardingKey字段已更新，且shardingKey属性值和修改值一致
 2、检查$shard索引对应字段同步修改，和shardingKey字段一致（直连数据组中主备节点，查看索引字段信息一致）</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1055,6 +985,131 @@
 2、a场景插入记录失败，查询原记录数正确；
 b场景插入记录成功，查询记录数正确；
 查询主备节点间数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sequoiadb集群运行正常
+2、系统中存在cs、主子表cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改主表属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主表修改shardingKey字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sequoiadb集群运行正常
+2、集群中存在cs、主表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、主表上修改shardingKey属性，分别验证如下场景：
+a、主表上没有子表
+b、主表上存在子表
+c、主表上去挂载所有子表
+2、检查修改结果
+3、检查$shard索引对应字段信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ac场景：1、修改成功，快照（snapshot（8））查看cl属性信息中shardingKey字段已更新，且shardingKey属性值和修改值一致
+2、检查$shard索引对应字段同步修改，和shardingKey字段一致（直连数据组中主备节点，查看索引字段信息一致）
+b场景：修改失败，返回不能修改等相关错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、可修改属性执行修改操作成功，快照（8）查看修改属性值为更新值
+2、不可修改属性执行修改失败，返回对应错误信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、开启压缩操作成功，查看cl属性信息中压缩类型默认为snappy（快照8查看编目节点上属性值已更新，直连数据节点快照4查看数据节点上属性已更新）
+2、数据插入成功，查询数据正确，查看数据按snappy方式压缩（和未开启压缩数据对比）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、开启压缩操作成功，查看cl属性信息中压缩类型为设置类型（快照8查看编目节点上属性值，直连数据节点快照4查看数据节点上属性）
+2、关闭压缩操作成功，查看cl属性信息中无压缩属性信息（快照8查看编目节点上属性值，直连数据节点快照4查看数据节点上属性）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、切分后，snapshot检查源组和目标组attribute:1,压缩类型为snappy（快照8查看编目节点上属性值，直连数据节点快照4查看数据节点上属性）
+2、关闭压缩后，快照查看cl属性中压缩未开启，查看原压缩数据未变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、开启压缩，修改压缩类型为lzw，分别验证如下场景：
+a、cl中没有数据，更新压缩类型为lzw
+b、cl中存在数据，更新压缩类型为lzw
+2、检查操作结果
+3、插入数据查看数据压缩情况
+4、查询数据，检查所有数据信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、场景ab：更新压缩类型成功，查看cl属性中压缩类型为lzw；（快照8查看编目节点上属性值，直连数据节点快照4查看数据节点上属性）
+2、插入数据后，查看数据有压缩（查看对应数据节点snapshot（4）中的DictionaryCreated参数为true）；数据组中所有节点上cl压缩类型一致
+3、dump数据日志文件查看日志中有记录修改前数据压缩类型为snappy，修改后插入数据压缩类型为lzw
+4、查询记录值正确，和插入数据信息一致（验证解压数据正常）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、使用setAttributes修改压缩类型为snappy，分别验证如下场景：
+a、cl中没有生成数据字典，更新压缩类型为snappy
+b、cl中存在数据字典，更新压缩类型为snappy
+2、检查操作结果
+3、插入数据，查看数据压缩情况
+4、查询数据，检查所有数据信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新压缩类型成功，查看cl属性中压缩类型为snappy（快照8查看编目节点上属性值）
+2、插入数据后，查看数据有压缩（查看对应数据节点snapshot（4）中的DictionaryCreated参数为false）；数据组中所有节点上cl压缩类型一致
+3、dump数据日志文件查看日志中有记录修改前数据压缩类型为lzw，修改后插入数据压缩类型为snappy
+4、查询记录值正确，和插入数据信息一致（验证解压数据正常）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、cl上设置压缩类型为lzw，插入数据刚好达到构建数据字典条件
+2、执行切分（切分后目标组上没有字典）
+3、修改压缩类型为snappy，检查操作结果
+4、插入新数据，dump数据日志查看数据压缩类型信息
+4、查询记录值正确，和插入数据信息一致（验证解压数据正常）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改压缩类型属性成功，查看cl属性中压缩类型为snappy类型（直连数据节点快照4查看数据节点上属性）
+2、dump数据日志查看源组上修改压缩类型前数据压缩类型为lzw，修改后为snappy，目标组上修改前记录没有压缩，修改压缩类型后记录压缩类型为snaapy
+3、查询记录值正确，和插入数据信息一致（验证解压数据正常）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、truncate操作成功，查看cl中数据为空；
+2、修改压缩类型操作成功，快照（8）查看cl属性信息中压缩类型为lzw，查看数据没有压缩字典（查看对应数据节点snapshot（4）中的DictionaryCreated参数为false）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、固定集合修改成功，快照(8)查看cl属性信息中Size值已更新，查看数据节点上cl属性信息已更新（快照4查看）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、固定集合修改成功，快照(8)查看cl属性信息中OverWrite值已更新，查看数据节点上cl属性信息已更新（快照4查看）
+2、插入记录成功，第一块的数据被覆盖，查询记录数不变
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改主表上属性信息，分别验证如下场景：
+a、主表上支持修改属性，如ReplSize、shardingKey、createIdIndex/dropIdIndex
+b、主表上不支持修改属性，如ShardingType、AutoSplit、Partition、Compressed等
+2、检查修改结果
+3、插入数据，检查操作结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1272,8 +1327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I57" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I59" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I59"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1592,13 +1647,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="4" customWidth="1"/>
     <col min="3" max="3" width="20.5" style="1" customWidth="1"/>
-    <col min="4" max="6" width="5" style="1" customWidth="1"/>
+    <col min="4" max="5" width="5" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="48.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="49.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="5.375" style="1" customWidth="1"/>
@@ -1688,10 +1744,10 @@
     </row>
     <row r="4" spans="1:9" ht="67.5">
       <c r="A4" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1703,10 +1759,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I4" s="3"/>
     </row>
@@ -1731,91 +1787,94 @@
         <v>18</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="54">
+    <row r="6" spans="1:9" ht="81">
       <c r="A6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="54">
+      <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="67.5">
-      <c r="A7" s="1" t="s">
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="67.5">
+      <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="54">
-      <c r="A8" s="1" t="s">
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="54">
+      <c r="A9" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" ht="67.5">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>21</v>
@@ -1830,36 +1889,34 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" ht="67.5">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="81">
-      <c r="A10" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
@@ -1867,51 +1924,51 @@
     </row>
     <row r="11" spans="1:9" ht="81">
       <c r="A11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="81">
+      <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="54">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
@@ -1919,7 +1976,7 @@
     </row>
     <row r="13" spans="1:9" ht="54">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -1934,48 +1991,48 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="54">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="81">
-      <c r="A14" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="81">
+      <c r="A15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="67.5">
-      <c r="A15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D15" s="3">
         <v>1</v>
       </c>
@@ -1986,10 +2043,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="I15" s="3">
         <v>1</v>
@@ -1997,10 +2054,10 @@
     </row>
     <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -2012,10 +2069,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I16" s="3">
         <v>1</v>
@@ -2023,10 +2080,10 @@
     </row>
     <row r="17" spans="1:9" ht="67.5">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -2038,10 +2095,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="I17" s="3">
         <v>1</v>
@@ -2049,33 +2106,33 @@
     </row>
     <row r="18" spans="1:9" ht="67.5">
       <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="67.5">
+      <c r="A19" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="54">
-      <c r="A19" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>21</v>
@@ -2090,57 +2147,57 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="54">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" ht="67.5">
-      <c r="A20" s="1" t="s">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" ht="67.5">
+      <c r="A21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="81">
-      <c r="A21" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>64</v>
@@ -2149,131 +2206,131 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="67.5">
+    <row r="22" spans="1:9" ht="81">
       <c r="A22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="67.5">
+      <c r="A23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="54">
-      <c r="A23" s="1" t="s">
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="54">
+      <c r="A24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="81">
-      <c r="A24" s="1" t="s">
+      <c r="I24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="81">
+      <c r="A25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
-        <v>2</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I24" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="67.5">
-      <c r="A25" s="1" t="s">
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="67.5">
+      <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="3">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3">
-        <v>2</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="I25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="81">
-      <c r="A26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="I26" s="3">
         <v>1</v>
@@ -2281,155 +2338,155 @@
     </row>
     <row r="27" spans="1:9" ht="81">
       <c r="A27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="81">
+      <c r="A28" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="3">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3">
-        <v>2</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="54">
-      <c r="A28" s="1" t="s">
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="54">
+      <c r="A29" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
-        <v>2</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I28" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="135">
-      <c r="A29" s="1" t="s">
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="135">
+      <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3">
-        <v>2</v>
-      </c>
-      <c r="F29" s="3">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I29" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="94.5">
-      <c r="A30" s="1" t="s">
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="94.5">
+      <c r="A31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3">
-        <v>2</v>
-      </c>
-      <c r="F30" s="3">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="67.5">
-      <c r="A31" s="1" t="s">
+      <c r="I31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="67.5">
+      <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3">
-        <v>2</v>
-      </c>
-      <c r="F31" s="3">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="I31" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="54">
-      <c r="A32" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="I32" s="3">
         <v>1</v>
@@ -2437,7 +2494,7 @@
     </row>
     <row r="33" spans="1:9" ht="54">
       <c r="A33" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>66</v>
@@ -2452,44 +2509,44 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="54">
+      <c r="A34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="94.5">
-      <c r="A34" s="1" t="s">
+      <c r="I34" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="94.5">
+      <c r="A35" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3">
-        <v>2</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I34" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="67.5">
-      <c r="A35" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
@@ -2504,10 +2561,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="I35" s="3">
         <v>1</v>
@@ -2515,88 +2572,88 @@
     </row>
     <row r="36" spans="1:9" ht="67.5">
       <c r="A36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2</v>
+      </c>
+      <c r="F36" s="3">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="67.5">
+      <c r="A37" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="H37" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="40.5">
+      <c r="A38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="3">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3">
-        <v>2</v>
-      </c>
-      <c r="F36" s="3">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="C38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="135">
+      <c r="A39" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="40.5">
-      <c r="A37" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="3">
-        <v>1</v>
-      </c>
-      <c r="E37" s="3">
-        <v>2</v>
-      </c>
-      <c r="F37" s="3">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="94.5">
-      <c r="A38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3">
-        <v>3</v>
-      </c>
-      <c r="F38" s="3">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I38" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="81">
-      <c r="A39" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
@@ -2608,44 +2665,44 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="I39" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="81">
+    <row r="40" spans="1:9" ht="121.5">
       <c r="A40" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
       </c>
       <c r="E40" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="3">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="I40" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="40.5">
+    <row r="41" spans="1:9" ht="108">
       <c r="A41" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
@@ -2660,199 +2717,201 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="40.5">
+      <c r="A42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="67.5">
+      <c r="A43" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="3">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="81">
+      <c r="A44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="3">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="108">
+      <c r="A45" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="3">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="54">
+      <c r="A46" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="67.5">
-      <c r="A42" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" s="3">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3">
-        <v>2</v>
-      </c>
-      <c r="F42" s="3">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I42" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="81">
-      <c r="A43" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="H46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="121.5">
+      <c r="A47" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="54">
+      <c r="A48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="3">
-        <v>1</v>
-      </c>
-      <c r="E43" s="3">
-        <v>2</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="108">
-      <c r="A44" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="3">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3">
-        <v>2</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="54">
-      <c r="A45" s="1" t="s">
+      <c r="D48" s="3">
+        <v>1</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="3">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="121.5">
-      <c r="A46" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3">
-        <v>2</v>
-      </c>
-      <c r="F46" s="3">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I46" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="54">
-      <c r="A47" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="3">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I47" s="3"/>
-    </row>
-    <row r="48" spans="1:9" ht="40.5">
-      <c r="A48" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D48" s="3">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="H48" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9" ht="94.5" customHeight="1">
+    <row r="49" spans="1:9" ht="40.5">
       <c r="A49" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -2864,21 +2923,19 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" ht="94.5" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -2890,10 +2947,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="I50" s="3">
         <v>1</v>
@@ -2901,10 +2958,10 @@
     </row>
     <row r="51" spans="1:9" ht="94.5" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -2916,10 +2973,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="I51" s="3">
         <v>1</v>
@@ -2927,122 +2984,174 @@
     </row>
     <row r="52" spans="1:9" ht="94.5" customHeight="1">
       <c r="A52" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="3">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="94.5" customHeight="1">
+      <c r="A53" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3">
+        <v>2</v>
+      </c>
+      <c r="F53" s="3">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I53" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="94.5">
+      <c r="A54" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2</v>
+      </c>
+      <c r="F54" s="3">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="94.5">
+      <c r="A55" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" s="3">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3">
+        <v>2</v>
+      </c>
+      <c r="F55" s="3">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I55" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="94.5" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D56" s="3">
+        <v>1</v>
+      </c>
+      <c r="E56" s="3">
+        <v>2</v>
+      </c>
+      <c r="F56" s="3">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="67.5">
+      <c r="A57" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" s="3">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="s">
+      <c r="H57" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H52" s="2" t="s">
+    </row>
+    <row r="58" spans="1:9" ht="202.5">
+      <c r="A58" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I52" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="94.5">
-      <c r="A53" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D53" s="3">
-        <v>1</v>
-      </c>
-      <c r="E53" s="3">
-        <v>2</v>
-      </c>
-      <c r="F53" s="3">
-        <v>1</v>
-      </c>
-      <c r="G53" s="2" t="s">
+    </row>
+    <row r="59" spans="1:9" ht="121.5">
+      <c r="A59" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I53" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="94.5" customHeight="1">
-      <c r="A54" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" s="3">
-        <v>1</v>
-      </c>
-      <c r="E54" s="3">
-        <v>2</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I54" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="67.5">
-      <c r="A55" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="202.5">
-      <c r="A56" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="121.5">
-      <c r="A57" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
